--- a/excel_sheeets/Somesula Manoj Kumar_L.xlsx
+++ b/excel_sheeets/Somesula Manoj Kumar_L.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
   <si>
     <t>Full Author Name</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t xml:space="preserve">Alias Name </t>
+  </si>
+  <si>
+    <t>Somesula</t>
   </si>
   <si>
     <t>Manoj Kumar</t>
@@ -221,7 +224,6 @@
     <font>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
@@ -289,41 +291,26 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -559,7 +546,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="36.44"/>
     <col customWidth="1" min="2" max="2" width="20.33"/>
-    <col customWidth="1" min="3" max="26" width="10.56"/>
+    <col customWidth="1" min="3" max="6" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -574,30 +561,30 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1"/>
@@ -1613,26 +1600,26 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="64.11"/>
     <col customWidth="1" min="2" max="2" width="31.33"/>
-    <col customWidth="1" min="3" max="26" width="10.56"/>
+    <col customWidth="1" min="3" max="6" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2">
         <v>6.0</v>
@@ -1646,7 +1633,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2">
         <v>1.0</v>
@@ -1660,7 +1647,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2">
         <v>2.0</v>
@@ -1674,7 +1661,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2">
         <v>1.0</v>
@@ -1687,8 +1674,8 @@
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>17</v>
+      <c r="A6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B6" s="2">
         <v>2.0</v>
@@ -2711,12 +2698,12 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="40.67"/>
     <col customWidth="1" min="2" max="2" width="23.0"/>
-    <col customWidth="1" min="3" max="26" width="10.56"/>
+    <col customWidth="1" min="3" max="6" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2">
         <v>118.0</v>
@@ -2724,15 +2711,15 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2">
         <v>6.0</v>
@@ -2740,32 +2727,32 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2">
-        <v>5.0</v>
+        <v>23</v>
+      </c>
+      <c r="B4" s="3">
+        <v>7.38</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2">
-        <v>7.38</v>
+        <v>24</v>
+      </c>
+      <c r="B5" s="3">
+        <v>118.0</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2">
-        <v>118.0</v>
+        <v>25</v>
+      </c>
+      <c r="B6" s="3">
+        <v>5.0</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2">
         <v>16.0</v>
@@ -2774,10 +2761,10 @@
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -3867,21 +3854,21 @@
     <col customWidth="1" min="2" max="2" width="19.33"/>
     <col customWidth="1" min="3" max="3" width="22.78"/>
     <col customWidth="1" min="4" max="4" width="36.78"/>
-    <col customWidth="1" min="5" max="26" width="10.56"/>
+    <col customWidth="1" min="5" max="6" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -4914,26 +4901,26 @@
     <col customWidth="1" min="1" max="1" width="134.33"/>
     <col customWidth="1" min="2" max="2" width="55.67"/>
     <col customWidth="1" min="3" max="3" width="22.78"/>
-    <col customWidth="1" min="4" max="26" width="10.56"/>
+    <col customWidth="1" min="4" max="6" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6">
         <v>2.0</v>
@@ -4942,10 +4929,10 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="6">
         <v>1.0</v>
@@ -4954,10 +4941,10 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="6">
         <v>2.0</v>
@@ -4966,10 +4953,10 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6">
         <v>3.0</v>
@@ -4978,10 +4965,10 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -4989,10 +4976,10 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2">
         <v>1.0</v>
@@ -5000,10 +4987,10 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2">
         <v>1.0</v>
@@ -5011,10 +4998,10 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2">
         <v>1.0</v>
@@ -5022,10 +5009,10 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2">
         <v>1.0</v>
@@ -5033,10 +5020,10 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
@@ -5044,257 +5031,257 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="9"/>
+      <c r="A13" s="8"/>
       <c r="C13" s="2">
         <f>SUM(C2:C12)</f>
         <v>15</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="9"/>
+      <c r="A14" s="8"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="9"/>
+      <c r="A15" s="8"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="9"/>
+      <c r="A16" s="8"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
+      <c r="A17" s="8"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
+      <c r="A19" s="8"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
+      <c r="A21" s="8"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
+      <c r="A23" s="8"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="B32" s="9"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="9"/>
-      <c r="B64" s="10"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="9"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
     </row>
     <row r="75" ht="15.75" customHeight="1"/>
     <row r="76" ht="15.75" customHeight="1"/>
@@ -6238,64 +6225,64 @@
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="41.0"/>
-    <col customWidth="1" min="2" max="26" width="10.56"/>
+    <col customWidth="1" min="2" max="6" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>54</v>
+      <c r="A2" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>55</v>
+      <c r="A3" s="10" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="11" t="s">
-        <v>56</v>
+      <c r="A4" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="12"/>
+      <c r="A5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="11"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="12"/>
+      <c r="A6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="11"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="12"/>
+      <c r="A7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="11"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="12"/>
+      <c r="A8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="11"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="12"/>
+      <c r="A9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="11"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="12"/>
+      <c r="A10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="11"/>
     </row>
     <row r="11" ht="15.75" customHeight="1"/>
     <row r="12" ht="15.75" customHeight="1"/>
